--- a/artfynd/A 20231-2023 artfynd.xlsx
+++ b/artfynd/A 20231-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 20231-2023 artfynd.xlsx
+++ b/artfynd/A 20231-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>78015619</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541841.1715154999</v>
+        <v>541841</v>
       </c>
       <c r="R2" t="n">
-        <v>6675248.179584512</v>
+        <v>6675248</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -760,19 +760,9 @@
           <t>2019-05-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-05-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 20231-2023 artfynd.xlsx
+++ b/artfynd/A 20231-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>78015619</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
